--- a/output/2026-08_품목신고보고현황.xlsx
+++ b/output/2026-08_품목신고보고현황.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="건강기능식품" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="일반식품" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DASHBOARD" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="건강기능식품" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일반식품" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,7 +55,7 @@
       <color rgb="00FF0000"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,18 @@
         <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,7 +121,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -65710,76 +65725,76 @@
           <t>전월대비</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="11" t="n">
         <v>106</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="H13" s="10" t="n">
+      <c r="H13" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I13" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="J13" s="10" t="n">
+      <c r="J13" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="K13" s="10" t="n">
+      <c r="K13" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="L13" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="M13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="10" t="n">
+      <c r="N13" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O13" s="10" t="n">
+      <c r="O13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="P13" s="10" t="n">
+      <c r="P13" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="Q13" s="10" t="n">
+      <c r="Q13" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="R13" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="S13" s="10" t="n">
+      <c r="S13" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="T13" s="10" t="n">
+      <c r="T13" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="U13" s="10" t="n">
+      <c r="U13" s="11" t="n">
         <v>73</v>
       </c>
-      <c r="V13" s="10" t="n">
+      <c r="V13" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="W13" s="10" t="n">
+      <c r="W13" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="X13" s="10" t="n">
+      <c r="X13" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="Y13" s="10" t="n">
+      <c r="Y13" s="11" t="n">
         <v>574</v>
       </c>
     </row>
@@ -65868,76 +65883,76 @@
           <t>전월대비</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="12" t="n">
         <v>-11</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="12" t="n">
         <v>-4</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="H15" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="I15" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="J15" s="12" t="n">
         <v>-5</v>
       </c>
-      <c r="K15" s="10" t="n">
+      <c r="K15" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="L15" s="12" t="n">
         <v>-3</v>
       </c>
       <c r="M15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="11" t="n">
+      <c r="N15" s="12" t="n">
         <v>-3</v>
       </c>
       <c r="O15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="11" t="n">
+      <c r="P15" s="12" t="n">
         <v>-21</v>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="12" t="n">
         <v>-1</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="R15" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="S15" s="10" t="n">
+      <c r="S15" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="T15" s="10" t="n">
+      <c r="T15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="U15" s="10" t="n">
+      <c r="U15" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="V15" s="11" t="n">
+      <c r="V15" s="12" t="n">
         <v>-5</v>
       </c>
-      <c r="W15" s="10" t="n">
+      <c r="W15" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="X15" s="10" t="n">
+      <c r="X15" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="Y15" s="10" t="n">
+      <c r="Y15" s="11" t="n">
         <v>30</v>
       </c>
     </row>
@@ -66026,76 +66041,76 @@
           <t>전월대비</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="12" t="n">
         <v>-15</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <v>-14</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <v>-53</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <v>-14</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="12" t="n">
         <v>-11</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="12" t="n">
         <v>-3</v>
       </c>
-      <c r="H17" s="11" t="n">
+      <c r="H17" s="12" t="n">
         <v>-23</v>
       </c>
-      <c r="I17" s="11" t="n">
+      <c r="I17" s="12" t="n">
         <v>-13</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J17" s="12" t="n">
         <v>-17</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="K17" s="12" t="n">
         <v>-12</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="L17" s="12" t="n">
         <v>-6</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="12" t="n">
         <v>-1</v>
       </c>
-      <c r="N17" s="11" t="n">
+      <c r="N17" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="O17" s="10" t="n">
+      <c r="O17" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="P17" s="11" t="n">
+      <c r="P17" s="12" t="n">
         <v>-20</v>
       </c>
-      <c r="Q17" s="11" t="n">
+      <c r="Q17" s="12" t="n">
         <v>-1</v>
       </c>
-      <c r="R17" s="11" t="n">
+      <c r="R17" s="12" t="n">
         <v>-11</v>
       </c>
-      <c r="S17" s="11" t="n">
+      <c r="S17" s="12" t="n">
         <v>-7</v>
       </c>
-      <c r="T17" s="11" t="n">
+      <c r="T17" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="U17" s="11" t="n">
+      <c r="U17" s="12" t="n">
         <v>-34</v>
       </c>
-      <c r="V17" s="11" t="n">
+      <c r="V17" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="W17" s="11" t="n">
+      <c r="W17" s="12" t="n">
         <v>-22</v>
       </c>
-      <c r="X17" s="11" t="n">
+      <c r="X17" s="12" t="n">
         <v>-7</v>
       </c>
-      <c r="Y17" s="11" t="n">
+      <c r="Y17" s="12" t="n">
         <v>-288</v>
       </c>
     </row>
@@ -66184,76 +66199,76 @@
           <t>전월대비</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="12" t="n">
         <v>-27</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="12" t="n">
         <v>-10</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="12" t="n">
         <v>-63</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>-15</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <v>-5</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="12" t="n">
         <v>-7</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" s="12" t="n">
         <v>-7</v>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="I19" s="12" t="n">
         <v>-8</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J19" s="12" t="n">
         <v>-29</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="K19" s="12" t="n">
         <v>-9</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="12" t="n">
         <v>-5</v>
       </c>
       <c r="M19" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="11" t="n">
+      <c r="N19" s="12" t="n">
         <v>-1</v>
       </c>
-      <c r="O19" s="11" t="n">
+      <c r="O19" s="12" t="n">
         <v>-3</v>
       </c>
-      <c r="P19" s="11" t="n">
+      <c r="P19" s="12" t="n">
         <v>-23</v>
       </c>
       <c r="Q19" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="12" t="n">
         <v>-9</v>
       </c>
-      <c r="S19" s="11" t="n">
+      <c r="S19" s="12" t="n">
         <v>-5</v>
       </c>
-      <c r="T19" s="11" t="n">
+      <c r="T19" s="12" t="n">
         <v>-3</v>
       </c>
-      <c r="U19" s="11" t="n">
+      <c r="U19" s="12" t="n">
         <v>-60</v>
       </c>
-      <c r="V19" s="11" t="n">
+      <c r="V19" s="12" t="n">
         <v>-18</v>
       </c>
-      <c r="W19" s="11" t="n">
+      <c r="W19" s="12" t="n">
         <v>-4</v>
       </c>
-      <c r="X19" s="11" t="n">
+      <c r="X19" s="12" t="n">
         <v>-5</v>
       </c>
-      <c r="Y19" s="11" t="n">
+      <c r="Y19" s="12" t="n">
         <v>-316</v>
       </c>
     </row>
@@ -67482,61 +67497,61 @@
           <t>전월대비</t>
         </is>
       </c>
-      <c r="B40" s="10" t="n">
+      <c r="B40" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="C40" s="10" t="n">
+      <c r="C40" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="E40" s="10" t="n">
+      <c r="E40" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="F40" s="10" t="n">
+      <c r="F40" s="11" t="n">
         <v>114</v>
       </c>
-      <c r="G40" s="10" t="n">
+      <c r="G40" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="H40" s="10" t="n">
+      <c r="H40" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="I40" s="10" t="n">
+      <c r="I40" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="J40" s="10" t="n">
+      <c r="J40" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="K40" s="10" t="n">
+      <c r="K40" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="L40" s="10" t="n">
+      <c r="L40" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="M40" s="10" t="n">
+      <c r="M40" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="N40" s="10" t="n">
+      <c r="N40" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="O40" s="10" t="n">
+      <c r="O40" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="P40" s="10" t="n">
+      <c r="P40" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="Q40" s="10" t="n">
+      <c r="Q40" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="R40" s="10" t="n">
+      <c r="R40" s="11" t="n">
         <v>42</v>
       </c>
-      <c r="S40" s="10" t="n">
+      <c r="S40" s="11" t="n">
         <v>1169</v>
       </c>
-      <c r="T40" s="10" t="n">
+      <c r="T40" s="11" t="n">
         <v>1775</v>
       </c>
     </row>
@@ -67610,61 +67625,61 @@
           <t>전월대비</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n">
+      <c r="B42" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C42" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="D42" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="12" t="n">
         <v>-8</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="12" t="n">
         <v>-8</v>
       </c>
-      <c r="G42" s="10" t="n">
+      <c r="G42" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="10" t="n">
+      <c r="H42" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="I42" s="10" t="n">
+      <c r="I42" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="10" t="n">
+      <c r="J42" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="K42" s="10" t="n">
+      <c r="K42" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="L42" s="11" t="n">
+      <c r="L42" s="12" t="n">
         <v>-6</v>
       </c>
-      <c r="M42" s="10" t="n">
+      <c r="M42" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="N42" s="10" t="n">
+      <c r="N42" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="O42" s="11" t="n">
+      <c r="O42" s="12" t="n">
         <v>-5</v>
       </c>
-      <c r="P42" s="10" t="n">
+      <c r="P42" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="Q42" s="10" t="n">
+      <c r="Q42" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="R42" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="S42" s="10" t="n">
+      <c r="S42" s="11" t="n">
         <v>115</v>
       </c>
-      <c r="T42" s="10" t="n">
+      <c r="T42" s="11" t="n">
         <v>290</v>
       </c>
     </row>
@@ -67738,61 +67753,61 @@
           <t>전월대비</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n">
+      <c r="B44" s="12" t="n">
         <v>-36</v>
       </c>
-      <c r="C44" s="11" t="n">
+      <c r="C44" s="12" t="n">
         <v>-68</v>
       </c>
-      <c r="D44" s="11" t="n">
+      <c r="D44" s="12" t="n">
         <v>-37</v>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="E44" s="12" t="n">
         <v>-18</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="F44" s="12" t="n">
         <v>-58</v>
       </c>
-      <c r="G44" s="11" t="n">
+      <c r="G44" s="12" t="n">
         <v>-4</v>
       </c>
-      <c r="H44" s="11" t="n">
+      <c r="H44" s="12" t="n">
         <v>-33</v>
       </c>
-      <c r="I44" s="11" t="n">
+      <c r="I44" s="12" t="n">
         <v>-20</v>
       </c>
-      <c r="J44" s="11" t="n">
+      <c r="J44" s="12" t="n">
         <v>-27</v>
       </c>
-      <c r="K44" s="11" t="n">
+      <c r="K44" s="12" t="n">
         <v>-22</v>
       </c>
-      <c r="L44" s="11" t="n">
+      <c r="L44" s="12" t="n">
         <v>-9</v>
       </c>
-      <c r="M44" s="11" t="n">
+      <c r="M44" s="12" t="n">
         <v>-62</v>
       </c>
-      <c r="N44" s="11" t="n">
+      <c r="N44" s="12" t="n">
         <v>-18</v>
       </c>
-      <c r="O44" s="11" t="n">
+      <c r="O44" s="12" t="n">
         <v>-5</v>
       </c>
-      <c r="P44" s="11" t="n">
+      <c r="P44" s="12" t="n">
         <v>-9</v>
       </c>
-      <c r="Q44" s="11" t="n">
+      <c r="Q44" s="12" t="n">
         <v>-13</v>
       </c>
-      <c r="R44" s="11" t="n">
+      <c r="R44" s="12" t="n">
         <v>-19</v>
       </c>
-      <c r="S44" s="11" t="n">
+      <c r="S44" s="12" t="n">
         <v>-668</v>
       </c>
-      <c r="T44" s="11" t="n">
+      <c r="T44" s="12" t="n">
         <v>-1126</v>
       </c>
     </row>
@@ -67866,61 +67881,61 @@
           <t>전월대비</t>
         </is>
       </c>
-      <c r="B46" s="11" t="n">
+      <c r="B46" s="12" t="n">
         <v>-37</v>
       </c>
-      <c r="C46" s="11" t="n">
+      <c r="C46" s="12" t="n">
         <v>-39</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="12" t="n">
         <v>-20</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="12" t="n">
         <v>-15</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="12" t="n">
         <v>-48</v>
       </c>
-      <c r="G46" s="11" t="n">
+      <c r="G46" s="12" t="n">
         <v>-3</v>
       </c>
-      <c r="H46" s="11" t="n">
+      <c r="H46" s="12" t="n">
         <v>-11</v>
       </c>
-      <c r="I46" s="11" t="n">
+      <c r="I46" s="12" t="n">
         <v>-13</v>
       </c>
-      <c r="J46" s="11" t="n">
+      <c r="J46" s="12" t="n">
         <v>-18</v>
       </c>
-      <c r="K46" s="11" t="n">
+      <c r="K46" s="12" t="n">
         <v>-8</v>
       </c>
-      <c r="L46" s="11" t="n">
+      <c r="L46" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="M46" s="11" t="n">
+      <c r="M46" s="12" t="n">
         <v>-52</v>
       </c>
-      <c r="N46" s="11" t="n">
+      <c r="N46" s="12" t="n">
         <v>-8</v>
       </c>
-      <c r="O46" s="11" t="n">
+      <c r="O46" s="12" t="n">
         <v>-4</v>
       </c>
-      <c r="P46" s="11" t="n">
+      <c r="P46" s="12" t="n">
         <v>-9</v>
       </c>
-      <c r="Q46" s="11" t="n">
+      <c r="Q46" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="R46" s="11" t="n">
+      <c r="R46" s="12" t="n">
         <v>-34</v>
       </c>
-      <c r="S46" s="11" t="n">
+      <c r="S46" s="12" t="n">
         <v>-616</v>
       </c>
-      <c r="T46" s="11" t="n">
+      <c r="T46" s="12" t="n">
         <v>-939</v>
       </c>
     </row>

--- a/output/2026-08_품목신고보고현황.xlsx
+++ b/output/2026-08_품목신고보고현황.xlsx
@@ -29746,7 +29746,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
@@ -32049,7 +32049,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -32237,7 +32237,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>효소</t>
         </is>
       </c>
     </row>
@@ -38253,7 +38253,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
@@ -38394,7 +38394,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
@@ -39005,7 +39005,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -40321,7 +40321,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
@@ -41731,7 +41731,7 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
@@ -42812,7 +42812,7 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -44316,7 +44316,7 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
@@ -44833,7 +44833,7 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -48546,7 +48546,7 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -51930,7 +51930,7 @@
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -52635,7 +52635,7 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>효소</t>
         </is>
       </c>
     </row>
@@ -52682,7 +52682,7 @@
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>효소</t>
         </is>
       </c>
     </row>
@@ -53904,7 +53904,7 @@
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -55878,7 +55878,7 @@
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -57570,7 +57570,7 @@
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -57852,7 +57852,7 @@
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
@@ -57993,7 +57993,7 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
@@ -60719,7 +60719,7 @@
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
@@ -67722,7 +67722,7 @@
       </c>
       <c r="I868" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -68051,7 +68051,7 @@
       </c>
       <c r="I875" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
@@ -70918,7 +70918,7 @@
       </c>
       <c r="I936" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
@@ -71200,7 +71200,7 @@
       </c>
       <c r="I942" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -72234,7 +72234,7 @@
       </c>
       <c r="I964" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
@@ -72375,7 +72375,7 @@
       </c>
       <c r="I967" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>효소</t>
         </is>
       </c>
     </row>
@@ -74208,7 +74208,7 @@
       </c>
       <c r="I1006" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>효소</t>
         </is>
       </c>
     </row>
@@ -75148,7 +75148,7 @@
       </c>
       <c r="I1026" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -76276,7 +76276,7 @@
       </c>
       <c r="I1050" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>프로바이오틱스</t>
         </is>
       </c>
     </row>
@@ -86809,58 +86809,58 @@
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="G39" s="10" t="n">
         <v>6</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L39" s="10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O39" s="10" t="n">
         <v>14</v>
       </c>
       <c r="P39" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q39" s="10" t="n">
         <v>9</v>
       </c>
       <c r="R39" s="10" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="S39" s="10" t="n">
-        <v>1072</v>
+        <v>1035</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>1673</v>
@@ -86873,58 +86873,58 @@
         </is>
       </c>
       <c r="B40" s="11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="G40" s="11" t="n">
         <v>6</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L40" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>14</v>
       </c>
       <c r="P40" s="11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q40" s="11" t="n">
         <v>9</v>
       </c>
       <c r="R40" s="11" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="S40" s="11" t="n">
-        <v>1072</v>
+        <v>1035</v>
       </c>
       <c r="T40" s="11" t="n">
         <v>1673</v>
@@ -86937,31 +86937,31 @@
         </is>
       </c>
       <c r="B41" s="10" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>7</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>33</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K41" s="10" t="n">
         <v>30</v>
@@ -86970,25 +86970,25 @@
         <v>11</v>
       </c>
       <c r="M41" s="10" t="n">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="O41" s="10" t="n">
         <v>9</v>
       </c>
       <c r="P41" s="10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q41" s="10" t="n">
         <v>15</v>
       </c>
       <c r="R41" s="10" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="S41" s="10" t="n">
-        <v>1171</v>
+        <v>1144</v>
       </c>
       <c r="T41" s="8" t="n">
         <v>1951</v>
@@ -87001,19 +87001,19 @@
         </is>
       </c>
       <c r="B42" s="11" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>-8</v>
+        <v>-18</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>1</v>
@@ -87022,37 +87022,37 @@
         <v>18</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="N42" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O42" s="12" t="n">
         <v>-5</v>
       </c>
       <c r="P42" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q42" s="11" t="n">
         <v>6</v>
       </c>
       <c r="R42" s="11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S42" s="11" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="T42" s="11" t="n">
         <v>278</v>
@@ -87065,19 +87065,19 @@
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>3</v>
@@ -87089,7 +87089,7 @@
         <v>18</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>15</v>
@@ -87098,10 +87098,10 @@
         <v>7</v>
       </c>
       <c r="M43" s="10" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O43" s="10" t="n">
         <v>6</v>
@@ -87113,10 +87113,10 @@
         <v>4</v>
       </c>
       <c r="R43" s="10" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="S43" s="10" t="n">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="T43" s="8" t="n">
         <v>1216</v>
@@ -87129,31 +87129,31 @@
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>-21</v>
+        <v>-25</v>
       </c>
       <c r="C44" s="12" t="n">
-        <v>-50</v>
+        <v>-57</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>-40</v>
+        <v>-48</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>-4</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>-30</v>
+        <v>-34</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>-15</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>-26</v>
+        <v>-29</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>-15</v>
@@ -87162,25 +87162,25 @@
         <v>-4</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>-44</v>
+        <v>-27</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="O44" s="12" t="n">
         <v>-3</v>
       </c>
       <c r="P44" s="12" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="Q44" s="12" t="n">
         <v>-11</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="S44" s="12" t="n">
-        <v>-418</v>
+        <v>-397</v>
       </c>
       <c r="T44" s="12" t="n">
         <v>-735</v>
@@ -87257,19 +87257,19 @@
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>-52</v>
+        <v>-54</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>-57</v>
+        <v>-59</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>-66</v>
+        <v>-68</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>-3</v>
@@ -87281,7 +87281,7 @@
         <v>-18</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>-15</v>
@@ -87290,10 +87290,10 @@
         <v>-7</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>-70</v>
+        <v>-57</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="O46" s="12" t="n">
         <v>-6</v>
@@ -87305,10 +87305,10 @@
         <v>-4</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>-49</v>
+        <v>-53</v>
       </c>
       <c r="S46" s="12" t="n">
-        <v>-753</v>
+        <v>-747</v>
       </c>
       <c r="T46" s="12" t="n">
         <v>-1216</v>

--- a/output/2026-08_품목신고보고현황.xlsx
+++ b/output/2026-08_품목신고보고현황.xlsx
@@ -27255,7 +27255,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -27490,7 +27490,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -31344,7 +31344,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -35527,7 +35527,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>남성건강</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>남성건강</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -41731,7 +41731,7 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -44833,7 +44833,7 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -49627,7 +49627,7 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -49768,7 +49768,7 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>수면</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -56066,7 +56066,7 @@
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -56395,7 +56395,7 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>효소</t>
         </is>
       </c>
     </row>
@@ -58087,7 +58087,7 @@
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>남성건강</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -63633,7 +63633,7 @@
       </c>
       <c r="I781" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -66406,7 +66406,7 @@
       </c>
       <c r="I840" t="inlineStr">
         <is>
-          <t>남성건강</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -67064,7 +67064,7 @@
       </c>
       <c r="I854" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -72328,7 +72328,7 @@
       </c>
       <c r="I966" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -74255,7 +74255,7 @@
       </c>
       <c r="I1007" t="inlineStr">
         <is>
-          <t>남성건강</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -86248,7 +86248,7 @@
         <v>46</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="D39" s="10" t="n">
         <v>62</v>
@@ -86257,19 +86257,19 @@
         <v>43</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G39" s="10" t="n">
         <v>6</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>19</v>
@@ -86278,10 +86278,10 @@
         <v>18</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O39" s="10" t="n">
         <v>14</v>
@@ -86296,7 +86296,7 @@
         <v>45</v>
       </c>
       <c r="S39" s="10" t="n">
-        <v>1026</v>
+        <v>999</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>1664</v>
@@ -86312,7 +86312,7 @@
         <v>46</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>62</v>
@@ -86321,19 +86321,19 @@
         <v>43</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G40" s="11" t="n">
         <v>6</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K40" s="11" t="n">
         <v>19</v>
@@ -86342,10 +86342,10 @@
         <v>18</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>14</v>
@@ -86360,7 +86360,7 @@
         <v>45</v>
       </c>
       <c r="S40" s="11" t="n">
-        <v>1026</v>
+        <v>999</v>
       </c>
       <c r="T40" s="11" t="n">
         <v>1664</v>
@@ -86376,22 +86376,22 @@
         <v>74</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>62</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>7</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>33</v>
@@ -86415,7 +86415,7 @@
         <v>9</v>
       </c>
       <c r="P41" s="10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q41" s="10" t="n">
         <v>15</v>
@@ -86424,7 +86424,7 @@
         <v>59</v>
       </c>
       <c r="S41" s="10" t="n">
-        <v>1139</v>
+        <v>1112</v>
       </c>
       <c r="T41" s="8" t="n">
         <v>1944</v>
@@ -86440,16 +86440,16 @@
         <v>28</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D42" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="12" t="n">
-        <v>-3</v>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>-21</v>
+        <v>-16</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>1</v>
@@ -86458,10 +86458,10 @@
         <v>18</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K42" s="11" t="n">
         <v>11</v>
@@ -86470,16 +86470,16 @@
         <v>-7</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N42" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O42" s="12" t="n">
         <v>-5</v>
       </c>
       <c r="P42" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q42" s="11" t="n">
         <v>6</v>
@@ -86504,16 +86504,16 @@
         <v>47</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D43" s="10" t="n">
         <v>34</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>3</v>
@@ -86525,16 +86525,16 @@
         <v>18</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L43" s="10" t="n">
         <v>7</v>
       </c>
       <c r="M43" s="10" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N43" s="10" t="n">
         <v>13</v>
@@ -86543,7 +86543,7 @@
         <v>6</v>
       </c>
       <c r="P43" s="10" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Q43" s="10" t="n">
         <v>4</v>
@@ -86552,7 +86552,7 @@
         <v>53</v>
       </c>
       <c r="S43" s="10" t="n">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="T43" s="8" t="n">
         <v>1204</v>
@@ -86568,37 +86568,37 @@
         <v>-27</v>
       </c>
       <c r="C44" s="12" t="n">
-        <v>-57</v>
+        <v>-65</v>
       </c>
       <c r="D44" s="12" t="n">
         <v>-28</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>-47</v>
+        <v>-49</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>-4</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>-34</v>
+        <v>-33</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>-15</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="L44" s="12" t="n">
         <v>-4</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>-27</v>
+        <v>-29</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>-19</v>
@@ -86607,7 +86607,7 @@
         <v>-3</v>
       </c>
       <c r="P44" s="12" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="Q44" s="12" t="n">
         <v>-11</v>
@@ -86616,7 +86616,7 @@
         <v>-6</v>
       </c>
       <c r="S44" s="12" t="n">
-        <v>-401</v>
+        <v>-382</v>
       </c>
       <c r="T44" s="12" t="n">
         <v>-740</v>
@@ -86696,16 +86696,16 @@
         <v>-47</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>-59</v>
+        <v>-76</v>
       </c>
       <c r="D46" s="12" t="n">
         <v>-34</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>-69</v>
+        <v>-68</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>-3</v>
@@ -86717,16 +86717,16 @@
         <v>-18</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>-7</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>-57</v>
+        <v>-55</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>-13</v>
@@ -86735,7 +86735,7 @@
         <v>-6</v>
       </c>
       <c r="P46" s="12" t="n">
-        <v>-18</v>
+        <v>-13</v>
       </c>
       <c r="Q46" s="12" t="n">
         <v>-4</v>
@@ -86744,7 +86744,7 @@
         <v>-53</v>
       </c>
       <c r="S46" s="12" t="n">
-        <v>-738</v>
+        <v>-730</v>
       </c>
       <c r="T46" s="12" t="n">
         <v>-1204</v>

--- a/output/2026-08_품목신고보고현황.xlsx
+++ b/output/2026-08_품목신고보고현황.xlsx
@@ -86245,7 +86245,7 @@
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" s="10" t="n">
         <v>101</v>
@@ -86263,7 +86263,7 @@
         <v>6</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>31</v>
@@ -86309,7 +86309,7 @@
         </is>
       </c>
       <c r="B40" s="11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="11" t="n">
         <v>101</v>
@@ -86327,7 +86327,7 @@
         <v>6</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I40" s="11" t="n">
         <v>31</v>
@@ -86385,13 +86385,13 @@
         <v>43</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>7</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>33</v>
@@ -86437,7 +86437,7 @@
         </is>
       </c>
       <c r="B42" s="11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C42" s="11" t="n">
         <v>40</v>
@@ -86449,13 +86449,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I42" s="11" t="n">
         <v>2</v>
@@ -86577,13 +86577,13 @@
         <v>-12</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>-49</v>
+        <v>-47</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>-4</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>-33</v>
+        <v>-35</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>-15</v>

--- a/output/2026-08_품목신고보고현황.xlsx
+++ b/output/2026-08_품목신고보고현황.xlsx
@@ -31767,7 +31767,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>혈행개선</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -47982,7 +47982,7 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>혈행개선</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -70072,7 +70072,7 @@
       </c>
       <c r="I918" t="inlineStr">
         <is>
-          <t>혈행개선</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -86259,14 +86259,14 @@
       <c r="F39" s="10" t="n">
         <v>133</v>
       </c>
-      <c r="G39" s="10" t="n">
-        <v>6</v>
+      <c r="G39" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H39" s="10" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>26</v>
@@ -86278,7 +86278,7 @@
         <v>18</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N39" s="10" t="n">
         <v>28</v>
@@ -86296,7 +86296,7 @@
         <v>45</v>
       </c>
       <c r="S39" s="10" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>1664</v>
@@ -86323,14 +86323,14 @@
       <c r="F40" s="11" t="n">
         <v>133</v>
       </c>
-      <c r="G40" s="11" t="n">
-        <v>6</v>
+      <c r="G40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J40" s="11" t="n">
         <v>26</v>
@@ -86342,7 +86342,7 @@
         <v>18</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N40" s="11" t="n">
         <v>28</v>
@@ -86360,7 +86360,7 @@
         <v>45</v>
       </c>
       <c r="S40" s="11" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="T40" s="11" t="n">
         <v>1664</v>
@@ -86379,7 +86379,7 @@
         <v>141</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>43</v>
@@ -86388,7 +86388,7 @@
         <v>115</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H41" s="10" t="n">
         <v>49</v>
@@ -86400,7 +86400,7 @@
         <v>49</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L41" s="10" t="n">
         <v>11</v>
@@ -86424,7 +86424,7 @@
         <v>59</v>
       </c>
       <c r="S41" s="10" t="n">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="T41" s="8" t="n">
         <v>1944</v>
@@ -86442,8 +86442,8 @@
       <c r="C42" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="D42" s="10" t="n">
-        <v>0</v>
+      <c r="D42" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
@@ -86452,25 +86452,25 @@
         <v>-18</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="11" t="n">
         <v>19</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="11" t="n">
         <v>23</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>-7</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N42" s="11" t="n">
         <v>4</v>
@@ -86488,7 +86488,7 @@
         <v>14</v>
       </c>
       <c r="S42" s="11" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="T42" s="11" t="n">
         <v>280</v>
@@ -86515,8 +86515,8 @@
       <c r="F43" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="G43" s="10" t="n">
-        <v>3</v>
+      <c r="G43" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H43" s="10" t="n">
         <v>14</v>
@@ -86552,7 +86552,7 @@
         <v>53</v>
       </c>
       <c r="S43" s="10" t="n">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="T43" s="8" t="n">
         <v>1204</v>
@@ -86571,7 +86571,7 @@
         <v>-65</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="E44" s="12" t="n">
         <v>-12</v>
@@ -86580,7 +86580,7 @@
         <v>-47</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>-35</v>
@@ -86592,7 +86592,7 @@
         <v>-31</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="L44" s="12" t="n">
         <v>-4</v>
@@ -86707,8 +86707,8 @@
       <c r="F46" s="12" t="n">
         <v>-68</v>
       </c>
-      <c r="G46" s="12" t="n">
-        <v>-3</v>
+      <c r="G46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>-14</v>
@@ -86744,7 +86744,7 @@
         <v>-53</v>
       </c>
       <c r="S46" s="12" t="n">
-        <v>-730</v>
+        <v>-733</v>
       </c>
       <c r="T46" s="12" t="n">
         <v>-1204</v>

--- a/output/2026-08_품목신고보고현황.xlsx
+++ b/output/2026-08_품목신고보고현황.xlsx
@@ -80271,7 +80271,7 @@
       </c>
       <c r="I1135" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>수면</t>
         </is>
       </c>
     </row>
@@ -86272,7 +86272,7 @@
         <v>26</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L39" s="10" t="n">
         <v>18</v>
@@ -86296,7 +86296,7 @@
         <v>45</v>
       </c>
       <c r="S39" s="10" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>1664</v>
@@ -86336,7 +86336,7 @@
         <v>26</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L40" s="11" t="n">
         <v>18</v>
@@ -86360,7 +86360,7 @@
         <v>45</v>
       </c>
       <c r="S40" s="11" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="T40" s="11" t="n">
         <v>1664</v>
@@ -86376,7 +86376,7 @@
         <v>74</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>63</v>
@@ -86400,13 +86400,13 @@
         <v>49</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L41" s="10" t="n">
         <v>11</v>
       </c>
       <c r="M41" s="10" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N41" s="10" t="n">
         <v>32</v>
@@ -86440,7 +86440,7 @@
         <v>29</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>1</v>
@@ -86464,13 +86464,13 @@
         <v>23</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>-7</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N42" s="11" t="n">
         <v>4</v>
@@ -86488,7 +86488,7 @@
         <v>14</v>
       </c>
       <c r="S42" s="11" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="T42" s="11" t="n">
         <v>280</v>
@@ -86528,7 +86528,7 @@
         <v>18</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L43" s="10" t="n">
         <v>7</v>
@@ -86552,7 +86552,7 @@
         <v>53</v>
       </c>
       <c r="S43" s="10" t="n">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="T43" s="8" t="n">
         <v>1204</v>
@@ -86568,7 +86568,7 @@
         <v>-27</v>
       </c>
       <c r="C44" s="12" t="n">
-        <v>-65</v>
+        <v>-64</v>
       </c>
       <c r="D44" s="12" t="n">
         <v>-29</v>
@@ -86592,13 +86592,13 @@
         <v>-31</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="L44" s="12" t="n">
         <v>-4</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>-19</v>
@@ -86616,7 +86616,7 @@
         <v>-6</v>
       </c>
       <c r="S44" s="12" t="n">
-        <v>-382</v>
+        <v>-383</v>
       </c>
       <c r="T44" s="12" t="n">
         <v>-740</v>
@@ -86720,7 +86720,7 @@
         <v>-18</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>-7</v>
@@ -86744,7 +86744,7 @@
         <v>-53</v>
       </c>
       <c r="S46" s="12" t="n">
-        <v>-733</v>
+        <v>-732</v>
       </c>
       <c r="T46" s="12" t="n">
         <v>-1204</v>

--- a/output/2026-08_품목신고보고현황.xlsx
+++ b/output/2026-08_품목신고보고현황.xlsx
@@ -38629,7 +38629,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
@@ -41402,7 +41402,7 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -43799,7 +43799,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
@@ -47512,7 +47512,7 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -47559,7 +47559,7 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -47606,7 +47606,7 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -47653,7 +47653,7 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -47700,7 +47700,7 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -48828,7 +48828,7 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
@@ -49392,7 +49392,7 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -52635,7 +52635,7 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -54421,7 +54421,7 @@
       </c>
       <c r="I585" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
@@ -57382,7 +57382,7 @@
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
@@ -61471,7 +61471,7 @@
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -63915,7 +63915,7 @@
       </c>
       <c r="I787" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -64526,7 +64526,7 @@
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
@@ -70354,7 +70354,7 @@
       </c>
       <c r="I924" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -74631,7 +74631,7 @@
       </c>
       <c r="I1015" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
@@ -76887,7 +76887,7 @@
       </c>
       <c r="I1063" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
@@ -77921,7 +77921,7 @@
       </c>
       <c r="I1085" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
@@ -78156,7 +78156,7 @@
       </c>
       <c r="I1090" t="inlineStr">
         <is>
-          <t>구강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -79049,7 +79049,7 @@
       </c>
       <c r="I1109" t="inlineStr">
         <is>
-          <t>프로바이오틱스</t>
+          <t>구강</t>
         </is>
       </c>
     </row>
@@ -86248,7 +86248,7 @@
         <v>45</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D39" s="10" t="n">
         <v>62</v>
@@ -86278,13 +86278,13 @@
         <v>18</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O39" s="10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P39" s="10" t="n">
         <v>14</v>
@@ -86296,7 +86296,7 @@
         <v>45</v>
       </c>
       <c r="S39" s="10" t="n">
-        <v>1002</v>
+        <v>1017</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>1664</v>
@@ -86312,7 +86312,7 @@
         <v>45</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>62</v>
@@ -86342,13 +86342,13 @@
         <v>18</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O40" s="11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P40" s="11" t="n">
         <v>14</v>
@@ -86360,7 +86360,7 @@
         <v>45</v>
       </c>
       <c r="S40" s="11" t="n">
-        <v>1002</v>
+        <v>1017</v>
       </c>
       <c r="T40" s="11" t="n">
         <v>1664</v>
@@ -86385,7 +86385,7 @@
         <v>43</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>2</v>
@@ -86406,13 +86406,13 @@
         <v>11</v>
       </c>
       <c r="M41" s="10" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="O41" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P41" s="10" t="n">
         <v>19</v>
@@ -86421,10 +86421,10 @@
         <v>15</v>
       </c>
       <c r="R41" s="10" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="S41" s="10" t="n">
-        <v>1115</v>
+        <v>1139</v>
       </c>
       <c r="T41" s="8" t="n">
         <v>1944</v>
@@ -86440,7 +86440,7 @@
         <v>29</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>1</v>
@@ -86449,7 +86449,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>2</v>
@@ -86470,13 +86470,13 @@
         <v>-7</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="N42" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P42" s="11" t="n">
         <v>5</v>
@@ -86485,10 +86485,10 @@
         <v>6</v>
       </c>
       <c r="R42" s="11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S42" s="11" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="T42" s="11" t="n">
         <v>280</v>
@@ -86534,10 +86534,10 @@
         <v>7</v>
       </c>
       <c r="M43" s="10" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O43" s="10" t="n">
         <v>6</v>
@@ -86552,7 +86552,7 @@
         <v>53</v>
       </c>
       <c r="S43" s="10" t="n">
-        <v>732</v>
+        <v>743</v>
       </c>
       <c r="T43" s="8" t="n">
         <v>1204</v>
@@ -86577,7 +86577,7 @@
         <v>-12</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>-47</v>
+        <v>-45</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>-2</v>
@@ -86598,13 +86598,13 @@
         <v>-4</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>-28</v>
+        <v>-26</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>-19</v>
+        <v>-7</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>-6</v>
@@ -86613,10 +86613,10 @@
         <v>-11</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="S44" s="12" t="n">
-        <v>-383</v>
+        <v>-396</v>
       </c>
       <c r="T44" s="12" t="n">
         <v>-740</v>
@@ -86726,10 +86726,10 @@
         <v>-7</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>-55</v>
+        <v>-46</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="O46" s="12" t="n">
         <v>-6</v>
@@ -86744,7 +86744,7 @@
         <v>-53</v>
       </c>
       <c r="S46" s="12" t="n">
-        <v>-732</v>
+        <v>-743</v>
       </c>
       <c r="T46" s="12" t="n">
         <v>-1204</v>

--- a/output/2026-08_품목신고보고현황.xlsx
+++ b/output/2026-08_품목신고보고현황.xlsx
@@ -48969,7 +48969,7 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>여성건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -60860,7 +60860,7 @@
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>모발</t>
         </is>
       </c>
     </row>
@@ -61988,7 +61988,7 @@
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>여성건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -67111,7 +67111,7 @@
       </c>
       <c r="I855" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>모발</t>
         </is>
       </c>
     </row>
@@ -86284,19 +86284,19 @@
         <v>15</v>
       </c>
       <c r="O39" s="10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="P39" s="10" t="n">
         <v>14</v>
       </c>
       <c r="Q39" s="10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>45</v>
       </c>
       <c r="S39" s="10" t="n">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>1664</v>
@@ -86348,19 +86348,19 @@
         <v>15</v>
       </c>
       <c r="O40" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="P40" s="11" t="n">
         <v>14</v>
       </c>
       <c r="Q40" s="11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R40" s="11" t="n">
         <v>45</v>
       </c>
       <c r="S40" s="11" t="n">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="T40" s="11" t="n">
         <v>1664</v>
@@ -86412,19 +86412,19 @@
         <v>18</v>
       </c>
       <c r="O41" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P41" s="10" t="n">
         <v>19</v>
       </c>
       <c r="Q41" s="10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>61</v>
       </c>
       <c r="S41" s="10" t="n">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="T41" s="8" t="n">
         <v>1944</v>
@@ -86476,19 +86476,19 @@
         <v>3</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="P42" s="11" t="n">
         <v>5</v>
       </c>
       <c r="Q42" s="11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R42" s="11" t="n">
         <v>16</v>
       </c>
       <c r="S42" s="11" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="T42" s="11" t="n">
         <v>280</v>
@@ -86540,13 +86540,13 @@
         <v>11</v>
       </c>
       <c r="O43" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P43" s="10" t="n">
         <v>13</v>
       </c>
       <c r="Q43" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>53</v>
@@ -86604,19 +86604,19 @@
         <v>-7</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>-6</v>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>-11</v>
+        <v>-16</v>
       </c>
       <c r="R44" s="12" t="n">
         <v>-8</v>
       </c>
       <c r="S44" s="12" t="n">
-        <v>-396</v>
+        <v>-394</v>
       </c>
       <c r="T44" s="12" t="n">
         <v>-740</v>
@@ -86732,13 +86732,13 @@
         <v>-11</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>-13</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="R46" s="12" t="n">
         <v>-53</v>
